--- a/sample-data/Employee report as on 2026-05-05.xlsx
+++ b/sample-data/Employee report as on 2026-05-05.xlsx
@@ -481,7 +481,7 @@
         <v>Female</v>
       </c>
       <c r="K2" t="str">
-        <v>2019-10-19</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L2" t="str">
         <v>Working</v>
@@ -531,7 +531,7 @@
         <v>Other</v>
       </c>
       <c r="K3" t="str">
-        <v>2019-04-05</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L3" t="str">
         <v>Working</v>
@@ -581,7 +581,7 @@
         <v>Male</v>
       </c>
       <c r="K4" t="str">
-        <v>2024-11-17</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L4" t="str">
         <v>Working</v>
@@ -631,7 +631,7 @@
         <v>Male</v>
       </c>
       <c r="K5" t="str">
-        <v>2018-11-02</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L5" t="str">
         <v>Working</v>
@@ -681,7 +681,7 @@
         <v>Male</v>
       </c>
       <c r="K6" t="str">
-        <v>2023-10-19</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L6" t="str">
         <v>Working</v>
@@ -731,7 +731,7 @@
         <v>Female</v>
       </c>
       <c r="K7" t="str">
-        <v>2023-02-06</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L7" t="str">
         <v>Working</v>
@@ -781,7 +781,7 @@
         <v>Female</v>
       </c>
       <c r="K8" t="str">
-        <v>2020-03-19</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L8" t="str">
         <v>Working</v>
@@ -831,7 +831,7 @@
         <v>Female</v>
       </c>
       <c r="K9" t="str">
-        <v>2017-01-05</v>
+        <v>2026-05-02</v>
       </c>
       <c r="L9" t="str">
         <v>Working</v>
@@ -960,7 +960,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-07-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E12" t="str">
         <v>Mumbai</v>
@@ -1410,7 +1410,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-07-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E21" t="str">
         <v>Remote</v>
@@ -2010,7 +2010,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-12-23</v>
+        <v>2026-05-19</v>
       </c>
       <c r="E33" t="str">
         <v>Bengaluru</v>
@@ -2260,7 +2260,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-12-22</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E38" t="str">
         <v>Delhi</v>
@@ -2610,7 +2610,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-11-21</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E45" t="str">
         <v>Mumbai</v>
@@ -2860,7 +2860,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-11-26</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E50" t="str">
         <v>Mumbai</v>
@@ -3560,7 +3560,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-09-17</v>
+        <v>2026-05-21</v>
       </c>
       <c r="E64" t="str">
         <v>Hyderabad</v>
@@ -4760,7 +4760,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D88" t="str">
-        <v>2025-11-19</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E88" t="str">
         <v>Hyderabad</v>
@@ -5110,7 +5110,7 @@
         <v>Airpay Academy Pvt Ltd</v>
       </c>
       <c r="D95" t="str">
-        <v>2025-09-16</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E95" t="str">
         <v>Hyderabad</v>
@@ -5360,7 +5360,7 @@
         <v>Airpay Payment Services Pvt Ltd</v>
       </c>
       <c r="D100" t="str">
-        <v>2025-09-22</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E100" t="str">
         <v>Delhi</v>

--- a/sample-data/Employee report as on 2026-05-05.xlsx
+++ b/sample-data/Employee report as on 2026-05-05.xlsx
@@ -457,7 +457,7 @@
         <v>Sneha Khan</v>
       </c>
       <c r="C2" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -507,7 +507,7 @@
         <v>Rohan Sharma</v>
       </c>
       <c r="C3" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -557,7 +557,7 @@
         <v>Ananya Mukherjee</v>
       </c>
       <c r="C4" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -607,7 +607,7 @@
         <v>Nikhil Desai</v>
       </c>
       <c r="C5" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -657,7 +657,7 @@
         <v>Manish Shah</v>
       </c>
       <c r="C6" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -707,7 +707,7 @@
         <v>Ishaan Nair</v>
       </c>
       <c r="C7" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -757,7 +757,7 @@
         <v>Rohit Mehta</v>
       </c>
       <c r="C8" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -807,7 +807,7 @@
         <v>Farhan Kulkarni</v>
       </c>
       <c r="C9" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Reyansh Banerjee</v>
       </c>
       <c r="C10" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -907,7 +907,7 @@
         <v>Vikram Singh</v>
       </c>
       <c r="C11" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -957,7 +957,7 @@
         <v>Manish Bose</v>
       </c>
       <c r="C12" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-07</v>
@@ -1007,7 +1007,7 @@
         <v>Rahul Pillai</v>
       </c>
       <c r="C13" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -1057,7 +1057,7 @@
         <v>Sneha Chopra</v>
       </c>
       <c r="C14" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -1107,7 +1107,7 @@
         <v>Sai Iyer</v>
       </c>
       <c r="C15" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -1157,7 +1157,7 @@
         <v>Ira Bhat</v>
       </c>
       <c r="C16" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -1207,7 +1207,7 @@
         <v>Zoya Iyer</v>
       </c>
       <c r="C17" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -1257,7 +1257,7 @@
         <v>Yash Menon</v>
       </c>
       <c r="C18" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -1307,7 +1307,7 @@
         <v>Priya Rao</v>
       </c>
       <c r="C19" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>Sara Banerjee</v>
       </c>
       <c r="C20" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -1407,7 +1407,7 @@
         <v>Karan Chopra</v>
       </c>
       <c r="C21" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-11</v>
@@ -1457,7 +1457,7 @@
         <v>Rohan Rao</v>
       </c>
       <c r="C22" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -1507,7 +1507,7 @@
         <v>Suresh Rao</v>
       </c>
       <c r="C23" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -1557,7 +1557,7 @@
         <v>Anika Lopes</v>
       </c>
       <c r="C24" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -1607,7 +1607,7 @@
         <v>Sara Nair</v>
       </c>
       <c r="C25" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -1657,7 +1657,7 @@
         <v>Rohit Shah</v>
       </c>
       <c r="C26" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D26" t="str">
         <v/>
@@ -1707,7 +1707,7 @@
         <v>Pari Joshi</v>
       </c>
       <c r="C27" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -1757,7 +1757,7 @@
         <v>Arjun Singh</v>
       </c>
       <c r="C28" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Vivaan Joshi</v>
       </c>
       <c r="C29" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -1857,7 +1857,7 @@
         <v>Tara Singh</v>
       </c>
       <c r="C30" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1907,7 +1907,7 @@
         <v>Sara Reddy</v>
       </c>
       <c r="C31" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1957,7 +1957,7 @@
         <v>Neha Banerjee</v>
       </c>
       <c r="C32" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -2007,7 +2007,7 @@
         <v>Ira Malhotra</v>
       </c>
       <c r="C33" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-19</v>
@@ -2057,7 +2057,7 @@
         <v>Myra Kumar</v>
       </c>
       <c r="C34" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D34" t="str">
         <v/>
@@ -2107,7 +2107,7 @@
         <v>Reyansh Chopra</v>
       </c>
       <c r="C35" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -2157,7 +2157,7 @@
         <v>Vikram Sharma</v>
       </c>
       <c r="C36" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -2207,7 +2207,7 @@
         <v>Zoya Sheikh</v>
       </c>
       <c r="C37" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -2257,7 +2257,7 @@
         <v>Aditya Das</v>
       </c>
       <c r="C38" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-21</v>
@@ -2307,7 +2307,7 @@
         <v>Anjali Menon</v>
       </c>
       <c r="C39" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -2357,7 +2357,7 @@
         <v>Amit Kulkarni</v>
       </c>
       <c r="C40" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D40" t="str">
         <v/>
@@ -2407,7 +2407,7 @@
         <v>Vihaan Iyer</v>
       </c>
       <c r="C41" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D41" t="str">
         <v/>
@@ -2457,7 +2457,7 @@
         <v>Rahul Pillai</v>
       </c>
       <c r="C42" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -2507,7 +2507,7 @@
         <v>Pari Bose</v>
       </c>
       <c r="C43" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D43" t="str">
         <v/>
@@ -2557,7 +2557,7 @@
         <v>Arjun Reddy</v>
       </c>
       <c r="C44" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D44" t="str">
         <v/>
@@ -2607,7 +2607,7 @@
         <v>Sai Singh</v>
       </c>
       <c r="C45" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-03</v>
@@ -2657,7 +2657,7 @@
         <v>Ira Khan</v>
       </c>
       <c r="C46" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D46" t="str">
         <v/>
@@ -2707,7 +2707,7 @@
         <v>Megha Sharma</v>
       </c>
       <c r="C47" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D47" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Karan Kumar</v>
       </c>
       <c r="C48" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -2807,7 +2807,7 @@
         <v>Saanvi Bose</v>
       </c>
       <c r="C49" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D49" t="str">
         <v/>
@@ -2857,7 +2857,7 @@
         <v>Kavya Mukherjee</v>
       </c>
       <c r="C50" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2907,7 +2907,7 @@
         <v>Diya Menon</v>
       </c>
       <c r="C51" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -2957,7 +2957,7 @@
         <v>Amit Desai</v>
       </c>
       <c r="C52" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D52" t="str">
         <v/>
@@ -3007,7 +3007,7 @@
         <v>Arjun Bhat</v>
       </c>
       <c r="C53" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D53" t="str">
         <v/>
@@ -3057,7 +3057,7 @@
         <v>Saanvi Rao</v>
       </c>
       <c r="C54" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D54" t="str">
         <v/>
@@ -3107,7 +3107,7 @@
         <v>Rohan Khan</v>
       </c>
       <c r="C55" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D55" t="str">
         <v/>
@@ -3157,7 +3157,7 @@
         <v>Amit Singh</v>
       </c>
       <c r="C56" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D56" t="str">
         <v/>
@@ -3207,7 +3207,7 @@
         <v>Diya Iyer</v>
       </c>
       <c r="C57" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>Deepak Naidu</v>
       </c>
       <c r="C58" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D58" t="str">
         <v/>
@@ -3307,7 +3307,7 @@
         <v>Arjun Kumar</v>
       </c>
       <c r="C59" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D59" t="str">
         <v/>
@@ -3357,7 +3357,7 @@
         <v>Pooja Khan</v>
       </c>
       <c r="C60" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D60" t="str">
         <v/>
@@ -3407,7 +3407,7 @@
         <v>Kavya Dsouza</v>
       </c>
       <c r="C61" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D61" t="str">
         <v/>
@@ -3457,7 +3457,7 @@
         <v>Saanvi Malhotra</v>
       </c>
       <c r="C62" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D62" t="str">
         <v/>
@@ -3507,7 +3507,7 @@
         <v>Suresh Malhotra</v>
       </c>
       <c r="C63" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D63" t="str">
         <v/>
@@ -3557,7 +3557,7 @@
         <v>Divya Desai</v>
       </c>
       <c r="C64" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-21</v>
@@ -3607,7 +3607,7 @@
         <v>Nikhil Bhat</v>
       </c>
       <c r="C65" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D65" t="str">
         <v/>
@@ -3657,7 +3657,7 @@
         <v>Aditya Sheikh</v>
       </c>
       <c r="C66" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D66" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Reyansh Patel</v>
       </c>
       <c r="C67" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D67" t="str">
         <v/>
@@ -3757,7 +3757,7 @@
         <v>Rohan Kulkarni</v>
       </c>
       <c r="C68" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D68" t="str">
         <v/>
@@ -3807,7 +3807,7 @@
         <v>Yash Shah</v>
       </c>
       <c r="C69" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D69" t="str">
         <v/>
@@ -3857,7 +3857,7 @@
         <v>Pooja Banerjee</v>
       </c>
       <c r="C70" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D70" t="str">
         <v/>
@@ -3907,7 +3907,7 @@
         <v>Meera Fernandes</v>
       </c>
       <c r="C71" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -3957,7 +3957,7 @@
         <v>Pari Naidu</v>
       </c>
       <c r="C72" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D72" t="str">
         <v/>
@@ -4007,7 +4007,7 @@
         <v>Meera Das</v>
       </c>
       <c r="C73" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D73" t="str">
         <v/>
@@ -4057,7 +4057,7 @@
         <v>Arjun Bhat</v>
       </c>
       <c r="C74" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D74" t="str">
         <v/>
@@ -4107,7 +4107,7 @@
         <v>Aditya Bose</v>
       </c>
       <c r="C75" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D75" t="str">
         <v/>
@@ -4157,7 +4157,7 @@
         <v>Imran Gupta</v>
       </c>
       <c r="C76" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D76" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>Sneha Mehta</v>
       </c>
       <c r="C77" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D77" t="str">
         <v/>
@@ -4257,7 +4257,7 @@
         <v>Divya Menon</v>
       </c>
       <c r="C78" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D78" t="str">
         <v/>
@@ -4307,7 +4307,7 @@
         <v>Anika Sharma</v>
       </c>
       <c r="C79" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -4357,7 +4357,7 @@
         <v>Kabir Banerjee</v>
       </c>
       <c r="C80" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D80" t="str">
         <v/>
@@ -4407,7 +4407,7 @@
         <v>Priya Menon</v>
       </c>
       <c r="C81" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D81" t="str">
         <v/>
@@ -4457,7 +4457,7 @@
         <v>Ritu Malhotra</v>
       </c>
       <c r="C82" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D82" t="str">
         <v/>
@@ -4507,7 +4507,7 @@
         <v>Amit Reddy</v>
       </c>
       <c r="C83" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D83" t="str">
         <v/>
@@ -4557,7 +4557,7 @@
         <v>Nikhil Verma</v>
       </c>
       <c r="C84" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D84" t="str">
         <v/>
@@ -4607,7 +4607,7 @@
         <v>Vikram Patel</v>
       </c>
       <c r="C85" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -4657,7 +4657,7 @@
         <v>Sara Kumar</v>
       </c>
       <c r="C86" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D86" t="str">
         <v/>
@@ -4707,7 +4707,7 @@
         <v>Nikhil Chopra</v>
       </c>
       <c r="C87" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D87" t="str">
         <v/>
@@ -4757,7 +4757,7 @@
         <v>Myra Kumar</v>
       </c>
       <c r="C88" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-17</v>
@@ -4807,7 +4807,7 @@
         <v>Anika Desai</v>
       </c>
       <c r="C89" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D89" t="str">
         <v/>
@@ -4857,7 +4857,7 @@
         <v>Vivaan Malhotra</v>
       </c>
       <c r="C90" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D90" t="str">
         <v/>
@@ -4907,7 +4907,7 @@
         <v>Aarohi Singh</v>
       </c>
       <c r="C91" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D91" t="str">
         <v/>
@@ -4957,7 +4957,7 @@
         <v>Riya Malhotra</v>
       </c>
       <c r="C92" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D92" t="str">
         <v/>
@@ -5007,7 +5007,7 @@
         <v>Krishna Lopes</v>
       </c>
       <c r="C93" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D93" t="str">
         <v/>
@@ -5057,7 +5057,7 @@
         <v>Aditya Shah</v>
       </c>
       <c r="C94" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D94" t="str">
         <v/>
@@ -5107,7 +5107,7 @@
         <v>Pooja Patel</v>
       </c>
       <c r="C95" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-26</v>
@@ -5157,7 +5157,7 @@
         <v>Sanjay Bhat</v>
       </c>
       <c r="C96" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D96" t="str">
         <v/>
@@ -5207,7 +5207,7 @@
         <v>Rohit Kumar</v>
       </c>
       <c r="C97" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D97" t="str">
         <v/>
@@ -5257,7 +5257,7 @@
         <v>Pari Desai</v>
       </c>
       <c r="C98" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D98" t="str">
         <v/>
@@ -5307,7 +5307,7 @@
         <v>Ira Sheikh</v>
       </c>
       <c r="C99" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D99" t="str">
         <v/>
@@ -5357,7 +5357,7 @@
         <v>Krishna Iyer</v>
       </c>
       <c r="C100" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-13</v>
@@ -5407,7 +5407,7 @@
         <v>Karan Mehta</v>
       </c>
       <c r="C101" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D101" t="str">
         <v/>
@@ -5457,7 +5457,7 @@
         <v>Kabir Desai</v>
       </c>
       <c r="C102" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D102" t="str">
         <v/>
@@ -5507,7 +5507,7 @@
         <v>Megha Mehta</v>
       </c>
       <c r="C103" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D103" t="str">
         <v/>
@@ -5557,7 +5557,7 @@
         <v>Navya Chopra</v>
       </c>
       <c r="C104" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D104" t="str">
         <v/>
@@ -5607,7 +5607,7 @@
         <v>Aarav Verma</v>
       </c>
       <c r="C105" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D105" t="str">
         <v/>
@@ -5657,7 +5657,7 @@
         <v>Zoya Desai</v>
       </c>
       <c r="C106" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D106" t="str">
         <v/>
@@ -5707,7 +5707,7 @@
         <v>Divya Nair</v>
       </c>
       <c r="C107" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D107" t="str">
         <v/>
@@ -5757,7 +5757,7 @@
         <v>Navya Mukherjee</v>
       </c>
       <c r="C108" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D108" t="str">
         <v/>
@@ -5807,7 +5807,7 @@
         <v>Pooja Bose</v>
       </c>
       <c r="C109" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D109" t="str">
         <v/>
@@ -5857,7 +5857,7 @@
         <v>Sara Sheikh</v>
       </c>
       <c r="C110" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D110" t="str">
         <v/>
@@ -5907,7 +5907,7 @@
         <v>Manish Kulkarni</v>
       </c>
       <c r="C111" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D111" t="str">
         <v/>
@@ -5957,7 +5957,7 @@
         <v>Navya Khan</v>
       </c>
       <c r="C112" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D112" t="str">
         <v/>
@@ -6007,7 +6007,7 @@
         <v>Kavya Reddy</v>
       </c>
       <c r="C113" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D113" t="str">
         <v/>
@@ -6057,7 +6057,7 @@
         <v>Sanjay Reddy</v>
       </c>
       <c r="C114" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D114" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>Amit Fernandes</v>
       </c>
       <c r="C115" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D115" t="str">
         <v/>
@@ -6157,7 +6157,7 @@
         <v>Dev Patel</v>
       </c>
       <c r="C116" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D116" t="str">
         <v/>
@@ -6207,7 +6207,7 @@
         <v>Sanjay Desai</v>
       </c>
       <c r="C117" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D117" t="str">
         <v/>
@@ -6257,7 +6257,7 @@
         <v>Ishaan Shah</v>
       </c>
       <c r="C118" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D118" t="str">
         <v/>
@@ -6307,7 +6307,7 @@
         <v>Ritu Menon</v>
       </c>
       <c r="C119" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D119" t="str">
         <v/>
@@ -6357,7 +6357,7 @@
         <v>Ira Banerjee</v>
       </c>
       <c r="C120" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D120" t="str">
         <v/>
@@ -6407,7 +6407,7 @@
         <v>Dev Joshi</v>
       </c>
       <c r="C121" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D121" t="str">
         <v/>
@@ -6457,7 +6457,7 @@
         <v>Megha Khan</v>
       </c>
       <c r="C122" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D122" t="str">
         <v/>
@@ -6507,7 +6507,7 @@
         <v>Arjun Mukherjee</v>
       </c>
       <c r="C123" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D123" t="str">
         <v/>
@@ -6557,7 +6557,7 @@
         <v>Rahul Kumar</v>
       </c>
       <c r="C124" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D124" t="str">
         <v/>
@@ -6607,7 +6607,7 @@
         <v>Nikhil Mukherjee</v>
       </c>
       <c r="C125" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D125" t="str">
         <v/>
@@ -6657,7 +6657,7 @@
         <v>Reyansh Khan</v>
       </c>
       <c r="C126" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D126" t="str">
         <v/>
@@ -6707,7 +6707,7 @@
         <v>Sanjay Singh</v>
       </c>
       <c r="C127" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D127" t="str">
         <v>2025-07-17</v>
@@ -6757,7 +6757,7 @@
         <v>Aarav Lopes</v>
       </c>
       <c r="C128" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D128" t="str">
         <v>2025-11-15</v>
@@ -6807,7 +6807,7 @@
         <v>Ananya Iyer</v>
       </c>
       <c r="C129" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D129" t="str">
         <v/>
@@ -6857,7 +6857,7 @@
         <v>Sara Singh</v>
       </c>
       <c r="C130" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D130" t="str">
         <v/>
@@ -6907,7 +6907,7 @@
         <v>Meera Desai</v>
       </c>
       <c r="C131" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D131" t="str">
         <v/>
@@ -6957,7 +6957,7 @@
         <v>Suresh Chopra</v>
       </c>
       <c r="C132" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D132" t="str">
         <v/>
@@ -7007,7 +7007,7 @@
         <v>Priya Lopes</v>
       </c>
       <c r="C133" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D133" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>Nikhil Nair</v>
       </c>
       <c r="C134" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D134" t="str">
         <v>2025-06-07</v>
@@ -7107,7 +7107,7 @@
         <v>Krishna Nair</v>
       </c>
       <c r="C135" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D135" t="str">
         <v/>
@@ -7157,7 +7157,7 @@
         <v>Sanjay Fernandes</v>
       </c>
       <c r="C136" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D136" t="str">
         <v/>
@@ -7207,7 +7207,7 @@
         <v>Megha Sheikh</v>
       </c>
       <c r="C137" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D137" t="str">
         <v/>
@@ -7257,7 +7257,7 @@
         <v>Aadhya Nair</v>
       </c>
       <c r="C138" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D138" t="str">
         <v/>
@@ -7307,7 +7307,7 @@
         <v>Suresh Singh</v>
       </c>
       <c r="C139" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D139" t="str">
         <v/>
@@ -7357,7 +7357,7 @@
         <v>Imran Menon</v>
       </c>
       <c r="C140" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D140" t="str">
         <v/>
@@ -7407,7 +7407,7 @@
         <v>Anika Lopes</v>
       </c>
       <c r="C141" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D141" t="str">
         <v/>
@@ -7457,7 +7457,7 @@
         <v>Pooja Mehta</v>
       </c>
       <c r="C142" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D142" t="str">
         <v/>
@@ -7507,7 +7507,7 @@
         <v>Vihaan Menon</v>
       </c>
       <c r="C143" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D143" t="str">
         <v/>
@@ -7557,7 +7557,7 @@
         <v>Sara Joshi</v>
       </c>
       <c r="C144" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D144" t="str">
         <v/>
@@ -7607,7 +7607,7 @@
         <v>Amit Mukherjee</v>
       </c>
       <c r="C145" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D145" t="str">
         <v/>
@@ -7657,7 +7657,7 @@
         <v>Rohit Gupta</v>
       </c>
       <c r="C146" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D146" t="str">
         <v/>
@@ -7707,7 +7707,7 @@
         <v>Sai Fernandes</v>
       </c>
       <c r="C147" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D147" t="str">
         <v/>
@@ -7757,7 +7757,7 @@
         <v>Priya Rao</v>
       </c>
       <c r="C148" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D148" t="str">
         <v/>
@@ -7807,7 +7807,7 @@
         <v>Kavya Bhat</v>
       </c>
       <c r="C149" t="str">
-        <v>Airpay Academy Pvt Ltd</v>
+        <v>Acme Academy Pvt Ltd</v>
       </c>
       <c r="D149" t="str">
         <v/>
@@ -7857,7 +7857,7 @@
         <v>Rohit Reddy</v>
       </c>
       <c r="C150" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D150" t="str">
         <v>2025-06-24</v>
@@ -7907,7 +7907,7 @@
         <v>Sanjay Reddy</v>
       </c>
       <c r="C151" t="str">
-        <v>Airpay Payment Services Pvt Ltd</v>
+        <v>Acme Payments Pvt Ltd</v>
       </c>
       <c r="D151" t="str">
         <v>2025-08-25</v>
